--- a/docs/dossiers/dossier-paris-9eme-arrondissement-3929f257.xlsx
+++ b/docs/dossiers/dossier-paris-9eme-arrondissement-3929f257.xlsx
@@ -2309,7 +2309,7 @@
       </c>
       <c r="B12" s="29" t="inlineStr">
         <is>
-          <t>292 600 € 4 877 €/m² Vente Restauration rapide 60 m² 60 m² Provence Opéra, Paris 9ème arrondissement (75009) Voir l'annonce</t>
+          <t>L’Enseigne Parisienne vous propose ces murs commerciaux libres à la vente, d’une surface totale de 60 m², situés rue Blanche, au cœur d’un secteur recherché et dynamique du 9ᵉ arrondissement de Paris. Le local bénéficie d’un environnement attractif, à proximité immédiate de nombreux commerces, bureaux et axes de passage, ainsi que d’une excellente desserte en transports en commun (métros et bus à proximité). Il développe une surface de 20 m² en rez-de-chaussée, complétée par des surfaces en sous-sol, offrant une configuration fonctionnelle pour de nombreuses activités commerciales ou professionnelles. Ces murs présentent une belle opportunité d’investissement ou d’exploitation et peuvent accueillir une large typologie d’activités. 💰 Prix de vente : 300 000 € 📞 Contactez-nous dès maintenant pour organiser une visite et saisir cette opportunité au cœur du 9ᵉ arrondissement de Paris.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-9eme-arrondissement-3929f257.xlsx
+++ b/docs/dossiers/dossier-paris-9eme-arrondissement-3929f257.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 08/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 09/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-9eme-arrondissement-3929f257.xlsx
+++ b/docs/dossiers/dossier-paris-9eme-arrondissement-3929f257.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 09/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 10/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-9eme-arrondissement-3929f257.xlsx
+++ b/docs/dossiers/dossier-paris-9eme-arrondissement-3929f257.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 10/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 11/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,75 % sur 20 ans, charges provisionnées), il reste environ 142 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), il reste environ 163 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.0475</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-paris-9eme-arrondissement-3929f257.xlsx
+++ b/docs/dossiers/dossier-paris-9eme-arrondissement-3929f257.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 11/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 12/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
